--- a/data/uppermoon77_all_raw.xlsx
+++ b/data/uppermoon77_all_raw.xlsx
@@ -446,7 +446,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>dtk</t>
+          <t>aomam</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -464,19 +464,19 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>dtk</t>
+          <t>aomam</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DT01MEI2026</t>
+          <t>AM01JULI2026</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -489,23 +489,23 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT01MEI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM01JULI2026</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>dtk</t>
+          <t>aomam</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DT02MEI2026</t>
+          <t>AM02JULI2026</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3850</v>
+        <v>588657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -514,23 +514,23 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT02MEI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM02JULI2026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>dtk</t>
+          <t>aomam</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DT03MEI2026</t>
+          <t>AM03JULI2026</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3850</v>
+        <v>588657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -539,23 +539,23 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT03MEI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM03JULI2026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>dtk</t>
+          <t>aomam</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DT04MEI2026</t>
+          <t>AM04JULI2026</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3850</v>
+        <v>588657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -564,23 +564,23 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT04MEI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM04JULI2026</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dtk</t>
+          <t>aomam</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DT05MEI2026</t>
+          <t>AM05JULI2026</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3850</v>
+        <v>588657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -589,23 +589,23 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT05MEI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM05JULI2026</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dtk</t>
+          <t>aomam</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DT06MEI2026</t>
+          <t>AM06JULI2026</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3850</v>
+        <v>588657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -614,23 +614,23 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT06MEI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM06JULI2026</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>dtk</t>
+          <t>aomam</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DT07MEI2026</t>
+          <t>AM07JULI2026</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3850</v>
+        <v>588657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -639,23 +639,23 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT07MEI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM07JULI2026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>dtk</t>
+          <t>aomam</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DT08MEI2026</t>
+          <t>AM08JULI2026</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3850</v>
+        <v>588657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -664,23 +664,23 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT08MEI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM08JULI2026</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>dtk</t>
+          <t>aomam</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DT09MEI2026</t>
+          <t>AM09JULI2026</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3850</v>
+        <v>588657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -689,23 +689,23 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT09MEI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM09JULI2026</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>dtk</t>
+          <t>aomam</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DT10MEI2026</t>
+          <t>AM10JULI2026</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3850</v>
+        <v>588657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -714,23 +714,23 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT10MEI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM10JULI2026</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>dtk</t>
+          <t>aomam</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DT11MEI2026</t>
+          <t>AM11JULI2026</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3850</v>
+        <v>588657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -739,23 +739,23 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT11MEI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM11JULI2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>dtk</t>
+          <t>aomam</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DT12MEI2026</t>
+          <t>AM12JULI2026</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3850</v>
+        <v>588657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -764,23 +764,23 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT12MEI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM12JULI2026</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>dtk</t>
+          <t>aomam</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DT13MEI2026</t>
+          <t>AM13JULI2026</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3850</v>
+        <v>588657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -789,23 +789,23 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT13MEI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM13JULI2026</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>dtk</t>
+          <t>aomam</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DT14MEI2026</t>
+          <t>AM14JULI2026</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3850</v>
+        <v>588657</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -814,23 +814,23 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT14MEI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM14JULI2026</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>dtk</t>
+          <t>aomam</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DT15MEI2026</t>
+          <t>AM15JULI2026</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3850</v>
+        <v>588657</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -839,23 +839,23 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT15MEI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM15JULI2026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>dtk</t>
+          <t>aomam</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DT16MEI2026</t>
+          <t>AM16JULI2026</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3850</v>
+        <v>588657</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -864,23 +864,23 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT16MEI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM16JULI2026</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>dtk</t>
+          <t>aomam</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DT17MEI2026</t>
+          <t>AM17JULI2026</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3850</v>
+        <v>588657</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -889,23 +889,23 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT17MEI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM17JULI2026</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>dtk</t>
+          <t>aomam</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DT18MEI2026</t>
+          <t>AM18JULI2026</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3850</v>
+        <v>588657</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -914,23 +914,23 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT18MEI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM18JULI2026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>dtk</t>
+          <t>aomam</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DT19MEI2026</t>
+          <t>AM19JULI2026</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3850</v>
+        <v>588657</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -939,23 +939,23 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT19MEI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM19JULI2026</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>dtk</t>
+          <t>aomam</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DT20MEI2026</t>
+          <t>AM20JULI2026</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3850</v>
+        <v>588657</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -964,23 +964,23 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT20MEI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM20JULI2026</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>dtk</t>
+          <t>aomam</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DT21MEI2026</t>
+          <t>AM21JULI2026</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3850</v>
+        <v>588657</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -989,23 +989,23 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT21MEI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM21JULI2026</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>dtk</t>
+          <t>aomam</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DT22MEI2026</t>
+          <t>AM22JULI2026</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3850</v>
+        <v>588657</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1014,23 +1014,23 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT22MEI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM22JULI2026</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>dtk</t>
+          <t>aomam</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DT23MEI2026</t>
+          <t>AM23JULI2026</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3850</v>
+        <v>588657</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1039,23 +1039,23 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT23MEI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM23JULI2026</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>dtk</t>
+          <t>aomam</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DT24MEI2026</t>
+          <t>AM24JULI2026</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3850</v>
+        <v>588657</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1064,23 +1064,23 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT24MEI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM24JULI2026</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>dtk</t>
+          <t>aomam</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DT25MEI2026</t>
+          <t>AM25JULI2026</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3850</v>
+        <v>588657</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1089,23 +1089,23 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT25MEI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM25JULI2026</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>dtk</t>
+          <t>aomam</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DT26MEI2026</t>
+          <t>AM26JULI2026</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3850</v>
+        <v>588657</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1114,23 +1114,23 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT26MEI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM26JULI2026</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>dtk</t>
+          <t>aomam</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DT27MEI2026</t>
+          <t>AM27JULI2026</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3850</v>
+        <v>588657</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1139,23 +1139,23 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT27MEI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM27JULI2026</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>dtk</t>
+          <t>aomam</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DT28MEI2026</t>
+          <t>AM28JULI2026</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3850</v>
+        <v>588657</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1164,23 +1164,23 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT28MEI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM28JULI2026</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dtk</t>
+          <t>aomam</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DT29MEI2026</t>
+          <t>AM29JULI2026</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3850</v>
+        <v>588657</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1189,23 +1189,23 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT29MEI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM29JULI2026</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dtk</t>
+          <t>aomam</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DT30MEI2026</t>
+          <t>AM30JULI2026</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3850</v>
+        <v>588657</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1214,23 +1214,23 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT30MEI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM30JULI2026</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dtk</t>
+          <t>aomam</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DT31MEI2026</t>
+          <t>AM31JULI2026</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3850</v>
+        <v>588657</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1239,14 +1239,14 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT31MEI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM31JULI2026</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dtk</t>
+          <t>aomam</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>14651</v>
+        <v>14655</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1264,14 +1264,14 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>aomam</t>
+          <t>oganic</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1289,19 +1289,19 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>aomam</t>
+          <t>oganic</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AM01JULI2026</t>
+          <t>OA01FEBRUARI2026</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1314,23 +1314,23 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM01JULI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA01FEBRUARI2026</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>aomam</t>
+          <t>oganic</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AM02JULI2026</t>
+          <t>OA02FEBRUARI2026</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>588657</v>
+        <v>3850</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1339,23 +1339,23 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM02JULI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA02FEBRUARI2026</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>aomam</t>
+          <t>oganic</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AM03JULI2026</t>
+          <t>OA03FEBRUARI2026</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>588657</v>
+        <v>3850</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1364,23 +1364,23 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM03JULI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA03FEBRUARI2026</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>aomam</t>
+          <t>oganic</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AM04JULI2026</t>
+          <t>OA04FEBRUARI2026</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>588657</v>
+        <v>3850</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1389,23 +1389,23 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM04JULI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA04FEBRUARI2026</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>aomam</t>
+          <t>oganic</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AM05JULI2026</t>
+          <t>OA05FEBRUARI2026</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>588657</v>
+        <v>3850</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1414,23 +1414,23 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM05JULI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA05FEBRUARI2026</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>aomam</t>
+          <t>oganic</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AM06JULI2026</t>
+          <t>OA06FEBRUARI2026</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>588657</v>
+        <v>3850</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1439,23 +1439,23 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM06JULI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA06FEBRUARI2026</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>aomam</t>
+          <t>oganic</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AM07JULI2026</t>
+          <t>OA07FEBRUARI2026</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>588657</v>
+        <v>3850</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1464,23 +1464,23 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM07JULI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA07FEBRUARI2026</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>aomam</t>
+          <t>oganic</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AM08JULI2026</t>
+          <t>OA08FEBRUARI2026</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>588657</v>
+        <v>3850</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1489,23 +1489,23 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM08JULI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA08FEBRUARI2026</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>aomam</t>
+          <t>oganic</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AM09JULI2026</t>
+          <t>OA09FEBRUARI2026</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>588657</v>
+        <v>3850</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1514,23 +1514,23 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM09JULI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA09FEBRUARI2026</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>aomam</t>
+          <t>oganic</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AM10JULI2026</t>
+          <t>OA10FEBRUARI2026</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>588657</v>
+        <v>3850</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1539,23 +1539,23 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM10JULI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA10FEBRUARI2026</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>aomam</t>
+          <t>oganic</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>AM11JULI2026</t>
+          <t>OA11FEBRUARI2026</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>588657</v>
+        <v>3850</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1564,23 +1564,23 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM11JULI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA11FEBRUARI2026</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>aomam</t>
+          <t>oganic</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AM12JULI2026</t>
+          <t>OA12FEBRUARI2026</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>588657</v>
+        <v>3850</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1589,23 +1589,23 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM12JULI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA12FEBRUARI2026</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>aomam</t>
+          <t>oganic</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AM13JULI2026</t>
+          <t>OA13FEBRUARI2026</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>588657</v>
+        <v>3850</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1614,23 +1614,23 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM13JULI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA13FEBRUARI2026</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>aomam</t>
+          <t>oganic</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AM14JULI2026</t>
+          <t>OA14FEBRUARI2026</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>588657</v>
+        <v>3850</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -1639,23 +1639,23 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM14JULI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA14FEBRUARI2026</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>aomam</t>
+          <t>oganic</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AM15JULI2026</t>
+          <t>OA15FEBRUARI2026</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>588657</v>
+        <v>3850</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -1664,23 +1664,23 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM15JULI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA15FEBRUARI2026</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>aomam</t>
+          <t>oganic</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AM16JULI2026</t>
+          <t>OA16FEBRUARI2026</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>588657</v>
+        <v>3850</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -1689,23 +1689,23 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM16JULI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA16FEBRUARI2026</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>aomam</t>
+          <t>oganic</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AM17JULI2026</t>
+          <t>OA17FEBRUARI2026</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>588657</v>
+        <v>3850</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -1714,23 +1714,23 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM17JULI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA17FEBRUARI2026</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>aomam</t>
+          <t>oganic</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>AM18JULI2026</t>
+          <t>OA18FEBRUARI2026</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>588657</v>
+        <v>3850</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -1739,23 +1739,23 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM18JULI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA18FEBRUARI2026</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>aomam</t>
+          <t>oganic</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>AM19JULI2026</t>
+          <t>OA19FEBRUARI2026</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>588657</v>
+        <v>3850</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -1764,23 +1764,23 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM19JULI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA19FEBRUARI2026</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>aomam</t>
+          <t>oganic</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AM20JULI2026</t>
+          <t>OA20FEBRUARI2026</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>588657</v>
+        <v>3850</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -1789,23 +1789,23 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM20JULI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA20FEBRUARI2026</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>aomam</t>
+          <t>oganic</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>AM21JULI2026</t>
+          <t>OA21FEBRUARI2026</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>588657</v>
+        <v>3850</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -1814,23 +1814,23 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM21JULI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA21FEBRUARI2026</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>aomam</t>
+          <t>oganic</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>AM22JULI2026</t>
+          <t>OA22FEBRUARI2026</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>588657</v>
+        <v>3850</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -1839,23 +1839,23 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM22JULI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA22FEBRUARI2026</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>aomam</t>
+          <t>oganic</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>AM23JULI2026</t>
+          <t>OA23FEBRUARI2026</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>588657</v>
+        <v>3850</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -1864,23 +1864,23 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM23JULI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA23FEBRUARI2026</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>aomam</t>
+          <t>oganic</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>AM24JULI2026</t>
+          <t>OA24FEBRUARI2026</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>588657</v>
+        <v>3850</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -1889,23 +1889,23 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM24JULI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA24FEBRUARI2026</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>aomam</t>
+          <t>oganic</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>AM25JULI2026</t>
+          <t>OA25FEBRUARI2026</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>588657</v>
+        <v>3850</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -1914,23 +1914,23 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM25JULI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA25FEBRUARI2026</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>aomam</t>
+          <t>oganic</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AM26JULI2026</t>
+          <t>OA26FEBRUARI2026</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>588657</v>
+        <v>3850</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -1939,23 +1939,23 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM26JULI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA26FEBRUARI2026</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>aomam</t>
+          <t>oganic</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AM27JULI2026</t>
+          <t>OA27FEBRUARI2026</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>588657</v>
+        <v>3850</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -1964,23 +1964,23 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM27JULI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA27FEBRUARI2026</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>aomam</t>
+          <t>oganic</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AM28JULI2026</t>
+          <t>OA28FEBRUARI2026</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>588657</v>
+        <v>3850</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -1989,23 +1989,23 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM28JULI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA28FEBRUARI2026</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>aomam</t>
+          <t>oganic</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AM29JULI2026</t>
+          <t>export_raw_to_sheets.py</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>588657</v>
+        <v>6930</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -2014,23 +2014,23 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM29JULI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/export_raw_to_sheets.py</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>aomam</t>
+          <t>oganic</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>AM30JULI2026</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>588657</v>
+        <v>14664</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -2039,23 +2039,23 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM30JULI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>aomam</t>
+          <t>fhero</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AM31JULI2026</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>588657</v>
+        <v>933</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -2064,23 +2064,23 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/AM31JULI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>aomam</t>
+          <t>fhero</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>FH01MARET2026</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>14655</v>
+        <v>3850</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -2089,23 +2089,23 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/aomam/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH01MARET2026</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ester</t>
+          <t>fhero</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>FH02MARET2026</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>933</v>
+        <v>3850</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -2114,23 +2114,23 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH02MARET2026</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ester</t>
+          <t>fhero</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ER01DESEMBER2026</t>
+          <t>FH03MARET2026</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>588661</v>
+        <v>3850</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -2139,23 +2139,23 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER01DESEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH03MARET2026</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ester</t>
+          <t>fhero</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ER02DESEMBER2026</t>
+          <t>FH04MARET2026</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>588661</v>
+        <v>3850</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -2164,23 +2164,23 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER02DESEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH04MARET2026</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ester</t>
+          <t>fhero</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ER03DESEMBER2026</t>
+          <t>FH05MARET2026</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>588661</v>
+        <v>3850</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -2189,23 +2189,23 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER03DESEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH05MARET2026</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ester</t>
+          <t>fhero</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ER04DESEMBER2026</t>
+          <t>FH06MARET2026</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>588661</v>
+        <v>3850</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -2214,23 +2214,23 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER04DESEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH06MARET2026</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ester</t>
+          <t>fhero</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ER05DESEMBER2026</t>
+          <t>FH07MARET2026</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>588661</v>
+        <v>3850</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -2239,23 +2239,23 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER05DESEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH07MARET2026</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ester</t>
+          <t>fhero</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ER06DESEMBER2026</t>
+          <t>FH08MARET2026</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>588661</v>
+        <v>3850</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -2264,23 +2264,23 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER06DESEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH08MARET2026</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ester</t>
+          <t>fhero</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ER07DESEMBER2026</t>
+          <t>FH09MARET2026</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>588661</v>
+        <v>3850</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -2289,23 +2289,23 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER07DESEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH09MARET2026</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ester</t>
+          <t>fhero</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ER08DESEMBER2026</t>
+          <t>FH10MARET2026</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>588661</v>
+        <v>3850</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -2314,23 +2314,23 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER08DESEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH10MARET2026</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ester</t>
+          <t>fhero</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ER09DESEMBER2026</t>
+          <t>FH11MARET2026</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>588661</v>
+        <v>3850</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -2339,23 +2339,23 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER09DESEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH11MARET2026</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ester</t>
+          <t>fhero</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ER10DESEMBER2026</t>
+          <t>FH12MARET2026</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>588661</v>
+        <v>3850</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -2364,23 +2364,23 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER10DESEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH12MARET2026</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ester</t>
+          <t>fhero</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ER11DESEMBER2026</t>
+          <t>FH13MARET2026</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>588661</v>
+        <v>3850</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -2389,23 +2389,23 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER11DESEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH13MARET2026</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ester</t>
+          <t>fhero</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ER12DESEMBER2026</t>
+          <t>FH14MARET2026</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>588661</v>
+        <v>3850</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -2414,23 +2414,23 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER12DESEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH14MARET2026</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ester</t>
+          <t>fhero</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ER13DESEMBER2026</t>
+          <t>FH15MARET2026</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>588661</v>
+        <v>3850</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -2439,23 +2439,23 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER13DESEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH15MARET2026</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ester</t>
+          <t>fhero</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ER14DESEMBER2026</t>
+          <t>FH16MARET2026</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>588661</v>
+        <v>3850</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -2464,23 +2464,23 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER14DESEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH16MARET2026</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ester</t>
+          <t>fhero</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ER15DESEMBER2026</t>
+          <t>FH17MARET2026</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>588661</v>
+        <v>3850</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -2489,23 +2489,23 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER15DESEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH17MARET2026</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ester</t>
+          <t>fhero</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ER16DESEMBER2026</t>
+          <t>FH18MARET2026</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>588661</v>
+        <v>3850</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -2514,23 +2514,23 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER16DESEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH18MARET2026</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ester</t>
+          <t>fhero</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ER17DESEMBER2026</t>
+          <t>FH19MARET2026</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>588661</v>
+        <v>3850</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -2539,23 +2539,23 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER17DESEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH19MARET2026</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ester</t>
+          <t>fhero</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ER18DESEMBER2026</t>
+          <t>FH20MARET2026</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>588661</v>
+        <v>3850</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -2564,23 +2564,23 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER18DESEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH20MARET2026</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ester</t>
+          <t>fhero</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ER19DESEMBER2026</t>
+          <t>FH21MARET2026</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>588661</v>
+        <v>3850</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -2589,23 +2589,23 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER19DESEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH21MARET2026</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ester</t>
+          <t>fhero</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ER20DESEMBER2026</t>
+          <t>FH22MARET2026</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>588661</v>
+        <v>3850</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -2614,23 +2614,23 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER20DESEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH22MARET2026</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ester</t>
+          <t>fhero</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ER21DESEMBER2026</t>
+          <t>FH23MARET2026</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>588661</v>
+        <v>3850</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -2639,23 +2639,23 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER21DESEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH23MARET2026</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ester</t>
+          <t>fhero</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ER22DESEMBER2026</t>
+          <t>FH24MARET2026</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>588661</v>
+        <v>3850</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -2664,23 +2664,23 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER22DESEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH24MARET2026</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ester</t>
+          <t>fhero</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ER23DESEMBER2026</t>
+          <t>FH25MARET2026</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>588661</v>
+        <v>3850</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -2689,23 +2689,23 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER23DESEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH25MARET2026</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ester</t>
+          <t>fhero</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ER24DESEMBER2026</t>
+          <t>FH26MARET2026</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>588661</v>
+        <v>3850</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -2714,23 +2714,23 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER24DESEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH26MARET2026</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ester</t>
+          <t>fhero</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ER25DESEMBER2026</t>
+          <t>FH27MARET2026</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>588661</v>
+        <v>3850</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -2739,23 +2739,23 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER25DESEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH27MARET2026</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ester</t>
+          <t>fhero</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ER26DESEMBER2026</t>
+          <t>FH28MARET2026</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>588661</v>
+        <v>3850</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -2764,23 +2764,23 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER26DESEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH28MARET2026</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ester</t>
+          <t>fhero</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ER27DESEMBER2026</t>
+          <t>FH29MARET2026</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>588661</v>
+        <v>3850</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -2789,23 +2789,23 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER27DESEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH29MARET2026</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ester</t>
+          <t>fhero</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ER28DESEMBER2026</t>
+          <t>FH30MARET2026</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>588661</v>
+        <v>3850</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -2814,23 +2814,23 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER28DESEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH30MARET2026</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ester</t>
+          <t>fhero</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ER29DESEMBER2026</t>
+          <t>FH31MARET2026</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>588661</v>
+        <v>3850</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -2839,23 +2839,23 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER29DESEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH31MARET2026</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ester</t>
+          <t>fhero</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ER30DESEMBER2026</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>588661</v>
+        <v>14455</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -2864,23 +2864,23 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER30DESEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ester</t>
+          <t>bodyslam</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ER31DESEMBER2026</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>588661</v>
+        <v>936</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -2889,23 +2889,23 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER31DESEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ester</t>
+          <t>bodyslam</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>BS01AGUSTUS2026</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>14663</v>
+        <v>588660</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS01AGUSTUS2026</t>
         </is>
       </c>
     </row>
@@ -2926,11 +2926,11 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>BS02AGUSTUS2026</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>936</v>
+        <v>588660</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS02AGUSTUS2026</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>BS01AGUSTUS2026</t>
+          <t>BS03AGUSTUS2026</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS01AGUSTUS2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS03AGUSTUS2026</t>
         </is>
       </c>
     </row>
@@ -2976,7 +2976,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>BS02AGUSTUS2026</t>
+          <t>BS04AGUSTUS2026</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS02AGUSTUS2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS04AGUSTUS2026</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>BS03AGUSTUS2026</t>
+          <t>BS05AGUSTUS2026</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS03AGUSTUS2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS05AGUSTUS2026</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>BS04AGUSTUS2026</t>
+          <t>BS06AGUSTUS2026</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS04AGUSTUS2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS06AGUSTUS2026</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>BS05AGUSTUS2026</t>
+          <t>BS07AGUSTUS2026</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS05AGUSTUS2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS07AGUSTUS2026</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>BS06AGUSTUS2026</t>
+          <t>BS08AGUSTUS2026</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS06AGUSTUS2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS08AGUSTUS2026</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>BS07AGUSTUS2026</t>
+          <t>BS09AGUSTUS2026</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS07AGUSTUS2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS09AGUSTUS2026</t>
         </is>
       </c>
     </row>
@@ -3126,7 +3126,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>BS08AGUSTUS2026</t>
+          <t>BS10AGUSTUS2026</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS08AGUSTUS2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS10AGUSTUS2026</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>BS09AGUSTUS2026</t>
+          <t>BS11AGUSTUS2026</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS09AGUSTUS2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS11AGUSTUS2026</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>BS10AGUSTUS2026</t>
+          <t>BS12AGUSTUS2026</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS10AGUSTUS2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS12AGUSTUS2026</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>BS11AGUSTUS2026</t>
+          <t>BS13AGUSTUS2026</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS11AGUSTUS2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS13AGUSTUS2026</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>BS12AGUSTUS2026</t>
+          <t>BS14AGUSTUS2026</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS12AGUSTUS2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS14AGUSTUS2026</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>BS13AGUSTUS2026</t>
+          <t>BS15AGUSTUS2026</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS13AGUSTUS2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS15AGUSTUS2026</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>BS14AGUSTUS2026</t>
+          <t>BS16AGUSTUS2026</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS14AGUSTUS2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS16AGUSTUS2026</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>BS15AGUSTUS2026</t>
+          <t>BS17AGUSTUS2026</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS15AGUSTUS2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS17AGUSTUS2026</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>BS16AGUSTUS2026</t>
+          <t>BS18AGUSTUS2026</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS16AGUSTUS2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS18AGUSTUS2026</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>BS17AGUSTUS2026</t>
+          <t>BS19AGUSTUS2026</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS17AGUSTUS2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS19AGUSTUS2026</t>
         </is>
       </c>
     </row>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>BS18AGUSTUS2026</t>
+          <t>BS20AGUSTUS2026</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS18AGUSTUS2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS20AGUSTUS2026</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>BS19AGUSTUS2026</t>
+          <t>BS21AGUSTUS2026</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS19AGUSTUS2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS21AGUSTUS2026</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>BS20AGUSTUS2026</t>
+          <t>BS22AGUSTUS2026</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS20AGUSTUS2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS22AGUSTUS2026</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>BS21AGUSTUS2026</t>
+          <t>BS23AGUSTUS2026</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS21AGUSTUS2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS23AGUSTUS2026</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>BS22AGUSTUS2026</t>
+          <t>BS24AGUSTUS2026</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS22AGUSTUS2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS24AGUSTUS2026</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>BS23AGUSTUS2026</t>
+          <t>BS25AGUSTUS2026</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS23AGUSTUS2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS25AGUSTUS2026</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>BS24AGUSTUS2026</t>
+          <t>BS26AGUSTUS2026</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS24AGUSTUS2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS26AGUSTUS2026</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>BS25AGUSTUS2026</t>
+          <t>BS27AGUSTUS2026</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS25AGUSTUS2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS27AGUSTUS2026</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>BS26AGUSTUS2026</t>
+          <t>BS28AGUSTUS2026</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS26AGUSTUS2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS28AGUSTUS2026</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>BS27AGUSTUS2026</t>
+          <t>BS29AGUSTUS2026</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS27AGUSTUS2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS29AGUSTUS2026</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>BS28AGUSTUS2026</t>
+          <t>BS30AGUSTUS2026</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS28AGUSTUS2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS30AGUSTUS2026</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>BS29AGUSTUS2026</t>
+          <t>BS31AGUSTUS2026</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS29AGUSTUS2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS31AGUSTUS2026</t>
         </is>
       </c>
     </row>
@@ -3676,11 +3676,11 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>BS30AGUSTUS2026</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>588660</v>
+        <v>14664</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -3689,23 +3689,23 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS30AGUSTUS2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>bodyslam</t>
+          <t>suppacha</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>BS31AGUSTUS2026</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>588660</v>
+        <v>936</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -3714,23 +3714,23 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/BS31AGUSTUS2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>bodyslam</t>
+          <t>suppacha</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>SH01SEPTEMBER2026</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>14664</v>
+        <v>588662</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -3739,23 +3739,23 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/bodyslam/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH01SEPTEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>jarvis</t>
+          <t>suppacha</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>SH02SEPTEMBER2026</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>934</v>
+        <v>588662</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -3764,23 +3764,23 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH02SEPTEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>jarvis</t>
+          <t>suppacha</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>JS01NOVEMBER2026</t>
+          <t>SH03SEPTEMBER2026</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>588661</v>
+        <v>588662</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -3789,23 +3789,23 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS01NOVEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH03SEPTEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>jarvis</t>
+          <t>suppacha</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>JS02NOVEMBER2026</t>
+          <t>SH04SEPTEMBER2026</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>588661</v>
+        <v>588662</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -3814,23 +3814,23 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS02NOVEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH04SEPTEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>jarvis</t>
+          <t>suppacha</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>JS03NOVEMBER2026</t>
+          <t>SH05SEPTEMBER2026</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>588661</v>
+        <v>588662</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -3839,23 +3839,23 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS03NOVEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH05SEPTEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>jarvis</t>
+          <t>suppacha</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>JS04NOVEMBER2026</t>
+          <t>SH06SEPTEMBER2026</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>588661</v>
+        <v>588662</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -3864,23 +3864,23 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS04NOVEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH06SEPTEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>jarvis</t>
+          <t>suppacha</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>JS05NOVEMBER2026</t>
+          <t>SH07SEPTEMBER2026</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>588661</v>
+        <v>588662</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -3889,23 +3889,23 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS05NOVEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH07SEPTEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>jarvis</t>
+          <t>suppacha</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>JS06NOVEMBER2026</t>
+          <t>SH08SEPTEMBER2026</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>588661</v>
+        <v>588662</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -3914,23 +3914,23 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS06NOVEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH08SEPTEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>jarvis</t>
+          <t>suppacha</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>JS07NOVEMBER2026</t>
+          <t>SH09SEPTEMBER2026</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>588661</v>
+        <v>588662</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -3939,23 +3939,23 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS07NOVEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH09SEPTEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>jarvis</t>
+          <t>suppacha</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>JS08NOVEMBER2026</t>
+          <t>SH10SEPTEMBER2026</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>588661</v>
+        <v>588662</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -3964,23 +3964,23 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS08NOVEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH10SEPTEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>jarvis</t>
+          <t>suppacha</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>JS09NOVEMBER2026</t>
+          <t>SH11SEPTEMBER2026</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>588661</v>
+        <v>588662</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -3989,23 +3989,23 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS09NOVEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH11SEPTEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>jarvis</t>
+          <t>suppacha</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>JS10NOVEMBER2026</t>
+          <t>SH12SEPTEMBER2026</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>588661</v>
+        <v>588662</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -4014,23 +4014,23 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS10NOVEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH12SEPTEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>jarvis</t>
+          <t>suppacha</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>JS11NOVEMBER2026</t>
+          <t>SH13SEPTEMBER2026</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>588661</v>
+        <v>588662</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -4039,23 +4039,23 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS11NOVEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH13SEPTEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>jarvis</t>
+          <t>suppacha</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>JS12NOVEMBER2026</t>
+          <t>SH14SEPTEMBER2026</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>588661</v>
+        <v>588662</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -4064,23 +4064,23 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS12NOVEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH14SEPTEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>jarvis</t>
+          <t>suppacha</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>JS13NOVEMBER2026</t>
+          <t>SH15SEPTEMBER2026</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>588661</v>
+        <v>588662</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -4089,23 +4089,23 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS13NOVEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH15SEPTEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>jarvis</t>
+          <t>suppacha</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>JS14NOVEMBER2026</t>
+          <t>SH16SEPTEMBER2026</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>588661</v>
+        <v>588662</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -4114,23 +4114,23 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS14NOVEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH16SEPTEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>jarvis</t>
+          <t>suppacha</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>JS15NOVEMBER2026</t>
+          <t>SH17SEPTEMBER2026</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>588661</v>
+        <v>588662</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -4139,23 +4139,23 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS15NOVEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH17SEPTEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>jarvis</t>
+          <t>suppacha</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>JS16NOVEMBER2026</t>
+          <t>SH18SEPTEMBER2026</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>588661</v>
+        <v>588662</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -4164,23 +4164,23 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS16NOVEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH18SEPTEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>jarvis</t>
+          <t>suppacha</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>JS17NOVEMBER2026</t>
+          <t>SH19SEPTEMBER2026</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>588661</v>
+        <v>588662</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -4189,23 +4189,23 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS17NOVEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH19SEPTEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>jarvis</t>
+          <t>suppacha</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>JS18NOVEMBER2026</t>
+          <t>SH20SEPTEMBER2026</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>588661</v>
+        <v>588662</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -4214,23 +4214,23 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS18NOVEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH20SEPTEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>jarvis</t>
+          <t>suppacha</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>JS19NOVEMBER2026</t>
+          <t>SH21SEPTEMBER2026</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>588661</v>
+        <v>588662</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -4239,23 +4239,23 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS19NOVEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH21SEPTEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>jarvis</t>
+          <t>suppacha</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>JS20NOVEMBER2026</t>
+          <t>SH22SEPTEMBER2026</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>588661</v>
+        <v>588662</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -4264,23 +4264,23 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS20NOVEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH22SEPTEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>jarvis</t>
+          <t>suppacha</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>JS21NOVEMBER2026</t>
+          <t>SH23SEPTEMBER2026</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>588661</v>
+        <v>588662</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -4289,23 +4289,23 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS21NOVEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH23SEPTEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>jarvis</t>
+          <t>suppacha</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>JS22NOVEMBER2026</t>
+          <t>SH24SEPTEMBER2026</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>588661</v>
+        <v>588662</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -4314,23 +4314,23 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS22NOVEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH24SEPTEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>jarvis</t>
+          <t>suppacha</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>JS23NOVEMBER2026</t>
+          <t>SH25SEPTEMBER2026</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>588661</v>
+        <v>588662</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -4339,23 +4339,23 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS23NOVEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH25SEPTEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>jarvis</t>
+          <t>suppacha</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>JS24NOVEMBER2026</t>
+          <t>SH26SEPTEMBER2026</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>588661</v>
+        <v>588662</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -4364,23 +4364,23 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS24NOVEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH26SEPTEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>jarvis</t>
+          <t>suppacha</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>JS25NOVEMBER2026</t>
+          <t>SH27SEPTEMBER2026</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>588661</v>
+        <v>588662</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -4389,23 +4389,23 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS25NOVEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH27SEPTEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>jarvis</t>
+          <t>suppacha</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>JS26NOVEMBER2026</t>
+          <t>SH28SEPTEMBER2026</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>588661</v>
+        <v>588662</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -4414,23 +4414,23 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS26NOVEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH28SEPTEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>jarvis</t>
+          <t>suppacha</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>JS27NOVEMBER2026</t>
+          <t>SH29SEPTEMBER2026</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>588661</v>
+        <v>588662</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -4439,23 +4439,23 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS27NOVEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH29SEPTEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>jarvis</t>
+          <t>suppacha</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>JS28NOVEMBER2026</t>
+          <t>SH30SEPTEMBER2026</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>588661</v>
+        <v>588662</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -4464,23 +4464,23 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS28NOVEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH30SEPTEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>jarvis</t>
+          <t>suppacha</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>JS29NOVEMBER2026</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>588661</v>
+        <v>14668</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -4489,23 +4489,23 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS29NOVEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>jarvis</t>
+          <t>sintho</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>JS30NOVEMBER2026</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>588661</v>
+        <v>934</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -4514,23 +4514,23 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS30NOVEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>jarvis</t>
+          <t>sintho</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>ST01APRIL2026</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>14664</v>
+        <v>3850</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -4539,23 +4539,23 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST01APRIL2026</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>fhero</t>
+          <t>sintho</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>ST02APRIL2026</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>933</v>
+        <v>3850</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -4564,19 +4564,19 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST02APRIL2026</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>fhero</t>
+          <t>sintho</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>FH01MARET2026</t>
+          <t>ST03APRIL2026</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -4589,19 +4589,19 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH01MARET2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST03APRIL2026</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>fhero</t>
+          <t>sintho</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>FH02MARET2026</t>
+          <t>ST04APRIL2026</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -4614,19 +4614,19 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH02MARET2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST04APRIL2026</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>fhero</t>
+          <t>sintho</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>FH03MARET2026</t>
+          <t>ST05APRIL2026</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -4639,19 +4639,19 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH03MARET2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST05APRIL2026</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>fhero</t>
+          <t>sintho</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>FH04MARET2026</t>
+          <t>ST06APRIL2026</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -4664,19 +4664,19 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH04MARET2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST06APRIL2026</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>fhero</t>
+          <t>sintho</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>FH05MARET2026</t>
+          <t>ST07APRIL2026</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -4689,19 +4689,19 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH05MARET2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST07APRIL2026</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>fhero</t>
+          <t>sintho</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>FH06MARET2026</t>
+          <t>ST08APRIL2026</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -4714,19 +4714,19 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH06MARET2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST08APRIL2026</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>fhero</t>
+          <t>sintho</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>FH07MARET2026</t>
+          <t>ST09APRIL2026</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -4739,19 +4739,19 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH07MARET2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST09APRIL2026</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>fhero</t>
+          <t>sintho</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>FH08MARET2026</t>
+          <t>ST10APRIL2026</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -4764,19 +4764,19 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH08MARET2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST10APRIL2026</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>fhero</t>
+          <t>sintho</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>FH09MARET2026</t>
+          <t>ST11APRIL2026</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -4789,19 +4789,19 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH09MARET2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST11APRIL2026</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>fhero</t>
+          <t>sintho</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>FH10MARET2026</t>
+          <t>ST12APRIL2026</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -4814,19 +4814,19 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH10MARET2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST12APRIL2026</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>fhero</t>
+          <t>sintho</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>FH11MARET2026</t>
+          <t>ST13APRIL2026</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -4839,19 +4839,19 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH11MARET2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST13APRIL2026</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>fhero</t>
+          <t>sintho</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>FH12MARET2026</t>
+          <t>ST14APRIL2026</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -4864,19 +4864,19 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH12MARET2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST14APRIL2026</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>fhero</t>
+          <t>sintho</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>FH13MARET2026</t>
+          <t>ST15APRIL2026</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -4889,19 +4889,19 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH13MARET2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST15APRIL2026</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>fhero</t>
+          <t>sintho</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>FH14MARET2026</t>
+          <t>ST16APRIL2026</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -4914,19 +4914,19 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH14MARET2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST16APRIL2026</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>fhero</t>
+          <t>sintho</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>FH15MARET2026</t>
+          <t>ST17APRIL2026</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -4939,19 +4939,19 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH15MARET2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST17APRIL2026</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>fhero</t>
+          <t>sintho</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>FH16MARET2026</t>
+          <t>ST18APRIL2026</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -4964,19 +4964,19 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH16MARET2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST18APRIL2026</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>fhero</t>
+          <t>sintho</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>FH17MARET2026</t>
+          <t>ST19APRIL2026</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -4989,19 +4989,19 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH17MARET2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST19APRIL2026</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>fhero</t>
+          <t>sintho</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>FH18MARET2026</t>
+          <t>ST20APRIL2026</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -5014,19 +5014,19 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH18MARET2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST20APRIL2026</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>fhero</t>
+          <t>sintho</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>FH19MARET2026</t>
+          <t>ST21APRIL2026</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -5039,19 +5039,19 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH19MARET2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST21APRIL2026</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>fhero</t>
+          <t>sintho</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>FH20MARET2026</t>
+          <t>ST22APRIL2026</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -5064,19 +5064,19 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH20MARET2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST22APRIL2026</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>fhero</t>
+          <t>sintho</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>FH21MARET2026</t>
+          <t>ST23APRIL2026</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -5089,19 +5089,19 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH21MARET2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST23APRIL2026</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>fhero</t>
+          <t>sintho</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>FH22MARET2026</t>
+          <t>ST24APRIL2026</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -5114,19 +5114,19 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH22MARET2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST24APRIL2026</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>fhero</t>
+          <t>sintho</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>FH23MARET2026</t>
+          <t>ST25APRIL2026</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -5139,19 +5139,19 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH23MARET2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST25APRIL2026</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>fhero</t>
+          <t>sintho</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>FH24MARET2026</t>
+          <t>ST26APRIL2026</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -5164,19 +5164,19 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH24MARET2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST26APRIL2026</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>fhero</t>
+          <t>sintho</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>FH25MARET2026</t>
+          <t>ST27APRIL2026</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -5189,19 +5189,19 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH25MARET2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST27APRIL2026</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>fhero</t>
+          <t>sintho</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>FH26MARET2026</t>
+          <t>ST28APRIL2026</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -5214,19 +5214,19 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH26MARET2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST28APRIL2026</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>fhero</t>
+          <t>sintho</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>FH27MARET2026</t>
+          <t>ST29APRIL2026</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -5239,19 +5239,19 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH27MARET2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST29APRIL2026</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>fhero</t>
+          <t>sintho</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>FH28MARET2026</t>
+          <t>ST30APRIL2026</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -5264,23 +5264,23 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH28MARET2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST30APRIL2026</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>fhero</t>
+          <t>sintho</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>FH29MARET2026</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>3850</v>
+        <v>14658</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -5289,23 +5289,23 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH29MARET2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>fhero</t>
+          <t>dtk</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>FH30MARET2026</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>3850</v>
+        <v>931</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -5314,19 +5314,19 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH30MARET2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>fhero</t>
+          <t>dtk</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>FH31MARET2026</t>
+          <t>DT01MEI2026</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -5339,23 +5339,23 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/FH31MARET2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT01MEI2026</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>fhero</t>
+          <t>dtk</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>DT02MEI2026</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>14455</v>
+        <v>3850</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -5364,23 +5364,23 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/fhero/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT02MEI2026</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>suppacha</t>
+          <t>dtk</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>DT03MEI2026</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>936</v>
+        <v>3850</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -5389,23 +5389,23 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT03MEI2026</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>suppacha</t>
+          <t>dtk</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>SH01SEPTEMBER2026</t>
+          <t>DT04MEI2026</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>588662</v>
+        <v>3850</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -5414,23 +5414,23 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH01SEPTEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT04MEI2026</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>suppacha</t>
+          <t>dtk</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>SH02SEPTEMBER2026</t>
+          <t>DT05MEI2026</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>588662</v>
+        <v>3850</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -5439,23 +5439,23 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH02SEPTEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT05MEI2026</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>suppacha</t>
+          <t>dtk</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>SH03SEPTEMBER2026</t>
+          <t>DT06MEI2026</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>588662</v>
+        <v>3850</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -5464,23 +5464,23 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH03SEPTEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT06MEI2026</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>suppacha</t>
+          <t>dtk</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>SH04SEPTEMBER2026</t>
+          <t>DT07MEI2026</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>588662</v>
+        <v>3850</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -5489,23 +5489,23 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH04SEPTEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT07MEI2026</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>suppacha</t>
+          <t>dtk</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>SH05SEPTEMBER2026</t>
+          <t>DT08MEI2026</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>588662</v>
+        <v>3850</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -5514,23 +5514,23 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH05SEPTEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT08MEI2026</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>suppacha</t>
+          <t>dtk</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>SH06SEPTEMBER2026</t>
+          <t>DT09MEI2026</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>588662</v>
+        <v>3850</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -5539,23 +5539,23 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH06SEPTEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT09MEI2026</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>suppacha</t>
+          <t>dtk</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>SH07SEPTEMBER2026</t>
+          <t>DT10MEI2026</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>588662</v>
+        <v>3850</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -5564,23 +5564,23 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH07SEPTEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT10MEI2026</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>suppacha</t>
+          <t>dtk</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>SH08SEPTEMBER2026</t>
+          <t>DT11MEI2026</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>588662</v>
+        <v>3850</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -5589,23 +5589,23 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH08SEPTEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT11MEI2026</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>suppacha</t>
+          <t>dtk</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>SH09SEPTEMBER2026</t>
+          <t>DT12MEI2026</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>588662</v>
+        <v>3850</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -5614,23 +5614,23 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH09SEPTEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT12MEI2026</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>suppacha</t>
+          <t>dtk</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>SH10SEPTEMBER2026</t>
+          <t>DT13MEI2026</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>588662</v>
+        <v>3850</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -5639,23 +5639,23 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH10SEPTEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT13MEI2026</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>suppacha</t>
+          <t>dtk</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>SH11SEPTEMBER2026</t>
+          <t>DT14MEI2026</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>588662</v>
+        <v>3850</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -5664,23 +5664,23 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH11SEPTEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT14MEI2026</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>suppacha</t>
+          <t>dtk</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>SH12SEPTEMBER2026</t>
+          <t>DT15MEI2026</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>588662</v>
+        <v>3850</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -5689,23 +5689,23 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH12SEPTEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT15MEI2026</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>suppacha</t>
+          <t>dtk</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>SH13SEPTEMBER2026</t>
+          <t>DT16MEI2026</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>588662</v>
+        <v>3850</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -5714,23 +5714,23 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH13SEPTEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT16MEI2026</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>suppacha</t>
+          <t>dtk</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>SH14SEPTEMBER2026</t>
+          <t>DT17MEI2026</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>588662</v>
+        <v>3850</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -5739,23 +5739,23 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH14SEPTEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT17MEI2026</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>suppacha</t>
+          <t>dtk</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>SH15SEPTEMBER2026</t>
+          <t>DT18MEI2026</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>588662</v>
+        <v>3850</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -5764,23 +5764,23 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH15SEPTEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT18MEI2026</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>suppacha</t>
+          <t>dtk</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>SH16SEPTEMBER2026</t>
+          <t>DT19MEI2026</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>588662</v>
+        <v>3850</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -5789,23 +5789,23 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH16SEPTEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT19MEI2026</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>suppacha</t>
+          <t>dtk</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>SH17SEPTEMBER2026</t>
+          <t>DT20MEI2026</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>588662</v>
+        <v>3850</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -5814,23 +5814,23 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH17SEPTEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT20MEI2026</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>suppacha</t>
+          <t>dtk</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>SH18SEPTEMBER2026</t>
+          <t>DT21MEI2026</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>588662</v>
+        <v>3850</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -5839,23 +5839,23 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH18SEPTEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT21MEI2026</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>suppacha</t>
+          <t>dtk</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>SH19SEPTEMBER2026</t>
+          <t>DT22MEI2026</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>588662</v>
+        <v>3850</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -5864,23 +5864,23 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH19SEPTEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT22MEI2026</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>suppacha</t>
+          <t>dtk</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>SH20SEPTEMBER2026</t>
+          <t>DT23MEI2026</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>588662</v>
+        <v>3850</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -5889,23 +5889,23 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH20SEPTEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT23MEI2026</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>suppacha</t>
+          <t>dtk</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>SH21SEPTEMBER2026</t>
+          <t>DT24MEI2026</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>588662</v>
+        <v>3850</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -5914,23 +5914,23 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH21SEPTEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT24MEI2026</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>suppacha</t>
+          <t>dtk</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>SH22SEPTEMBER2026</t>
+          <t>DT25MEI2026</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>588662</v>
+        <v>3850</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -5939,23 +5939,23 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH22SEPTEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT25MEI2026</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>suppacha</t>
+          <t>dtk</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>SH23SEPTEMBER2026</t>
+          <t>DT26MEI2026</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>588662</v>
+        <v>3850</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -5964,23 +5964,23 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH23SEPTEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT26MEI2026</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>suppacha</t>
+          <t>dtk</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>SH24SEPTEMBER2026</t>
+          <t>DT27MEI2026</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>588662</v>
+        <v>3850</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -5989,23 +5989,23 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH24SEPTEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT27MEI2026</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>suppacha</t>
+          <t>dtk</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>SH25SEPTEMBER2026</t>
+          <t>DT28MEI2026</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>588662</v>
+        <v>3850</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -6014,23 +6014,23 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH25SEPTEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT28MEI2026</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>suppacha</t>
+          <t>dtk</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>SH26SEPTEMBER2026</t>
+          <t>DT29MEI2026</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>588662</v>
+        <v>3850</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -6039,23 +6039,23 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH26SEPTEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT29MEI2026</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>suppacha</t>
+          <t>dtk</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>SH27SEPTEMBER2026</t>
+          <t>DT30MEI2026</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>588662</v>
+        <v>3850</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -6064,23 +6064,23 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH27SEPTEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT30MEI2026</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>suppacha</t>
+          <t>dtk</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>SH28SEPTEMBER2026</t>
+          <t>DT31MEI2026</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>588662</v>
+        <v>3850</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -6089,23 +6089,23 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH28SEPTEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/DT31MEI2026</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>suppacha</t>
+          <t>dtk</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>SH29SEPTEMBER2026</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>588662</v>
+        <v>14651</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -6114,23 +6114,23 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH29SEPTEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/dtk/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>suppacha</t>
+          <t>jarvis</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>SH30SEPTEMBER2026</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>588662</v>
+        <v>934</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -6139,23 +6139,23 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/SH30SEPTEMBER2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>suppacha</t>
+          <t>jarvis</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>JS01NOVEMBER2026</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>14668</v>
+        <v>588661</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -6164,23 +6164,23 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppacha/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS01NOVEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>oganic</t>
+          <t>jarvis</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>JS02NOVEMBER2026</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>934</v>
+        <v>588661</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -6189,23 +6189,23 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS02NOVEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>oganic</t>
+          <t>jarvis</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>OA01FEBRUARI2026</t>
+          <t>JS03NOVEMBER2026</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -6214,23 +6214,23 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA01FEBRUARI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS03NOVEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>oganic</t>
+          <t>jarvis</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>OA02FEBRUARI2026</t>
+          <t>JS04NOVEMBER2026</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -6239,23 +6239,23 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA02FEBRUARI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS04NOVEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>oganic</t>
+          <t>jarvis</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>OA03FEBRUARI2026</t>
+          <t>JS05NOVEMBER2026</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -6264,23 +6264,23 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA03FEBRUARI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS05NOVEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>oganic</t>
+          <t>jarvis</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>OA04FEBRUARI2026</t>
+          <t>JS06NOVEMBER2026</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -6289,23 +6289,23 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA04FEBRUARI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS06NOVEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>oganic</t>
+          <t>jarvis</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>OA05FEBRUARI2026</t>
+          <t>JS07NOVEMBER2026</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -6314,23 +6314,23 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA05FEBRUARI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS07NOVEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>oganic</t>
+          <t>jarvis</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>OA06FEBRUARI2026</t>
+          <t>JS08NOVEMBER2026</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -6339,23 +6339,23 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA06FEBRUARI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS08NOVEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>oganic</t>
+          <t>jarvis</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>OA07FEBRUARI2026</t>
+          <t>JS09NOVEMBER2026</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -6364,23 +6364,23 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA07FEBRUARI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS09NOVEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>oganic</t>
+          <t>jarvis</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>OA08FEBRUARI2026</t>
+          <t>JS10NOVEMBER2026</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -6389,23 +6389,23 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA08FEBRUARI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS10NOVEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>oganic</t>
+          <t>jarvis</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>OA09FEBRUARI2026</t>
+          <t>JS11NOVEMBER2026</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -6414,23 +6414,23 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA09FEBRUARI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS11NOVEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>oganic</t>
+          <t>jarvis</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>OA10FEBRUARI2026</t>
+          <t>JS12NOVEMBER2026</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -6439,23 +6439,23 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA10FEBRUARI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS12NOVEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>oganic</t>
+          <t>jarvis</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>OA11FEBRUARI2026</t>
+          <t>JS13NOVEMBER2026</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -6464,23 +6464,23 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA11FEBRUARI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS13NOVEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>oganic</t>
+          <t>jarvis</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>OA12FEBRUARI2026</t>
+          <t>JS14NOVEMBER2026</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -6489,23 +6489,23 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA12FEBRUARI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS14NOVEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>oganic</t>
+          <t>jarvis</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>OA13FEBRUARI2026</t>
+          <t>JS15NOVEMBER2026</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -6514,23 +6514,23 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA13FEBRUARI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS15NOVEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>oganic</t>
+          <t>jarvis</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>OA14FEBRUARI2026</t>
+          <t>JS16NOVEMBER2026</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -6539,23 +6539,23 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA14FEBRUARI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS16NOVEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>oganic</t>
+          <t>jarvis</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>OA15FEBRUARI2026</t>
+          <t>JS17NOVEMBER2026</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -6564,23 +6564,23 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA15FEBRUARI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS17NOVEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>oganic</t>
+          <t>jarvis</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>OA16FEBRUARI2026</t>
+          <t>JS18NOVEMBER2026</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -6589,23 +6589,23 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA16FEBRUARI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS18NOVEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>oganic</t>
+          <t>jarvis</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>OA17FEBRUARI2026</t>
+          <t>JS19NOVEMBER2026</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -6614,23 +6614,23 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA17FEBRUARI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS19NOVEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>oganic</t>
+          <t>jarvis</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>OA18FEBRUARI2026</t>
+          <t>JS20NOVEMBER2026</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -6639,23 +6639,23 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA18FEBRUARI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS20NOVEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>oganic</t>
+          <t>jarvis</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>OA19FEBRUARI2026</t>
+          <t>JS21NOVEMBER2026</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -6664,23 +6664,23 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA19FEBRUARI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS21NOVEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>oganic</t>
+          <t>jarvis</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>OA20FEBRUARI2026</t>
+          <t>JS22NOVEMBER2026</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -6689,23 +6689,23 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA20FEBRUARI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS22NOVEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>oganic</t>
+          <t>jarvis</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>OA21FEBRUARI2026</t>
+          <t>JS23NOVEMBER2026</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -6714,23 +6714,23 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA21FEBRUARI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS23NOVEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>oganic</t>
+          <t>jarvis</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>OA22FEBRUARI2026</t>
+          <t>JS24NOVEMBER2026</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -6739,23 +6739,23 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA22FEBRUARI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS24NOVEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>oganic</t>
+          <t>jarvis</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>OA23FEBRUARI2026</t>
+          <t>JS25NOVEMBER2026</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -6764,23 +6764,23 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA23FEBRUARI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS25NOVEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>oganic</t>
+          <t>jarvis</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>OA24FEBRUARI2026</t>
+          <t>JS26NOVEMBER2026</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -6789,23 +6789,23 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA24FEBRUARI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS26NOVEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>oganic</t>
+          <t>jarvis</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>OA25FEBRUARI2026</t>
+          <t>JS27NOVEMBER2026</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -6814,23 +6814,23 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA25FEBRUARI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS27NOVEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>oganic</t>
+          <t>jarvis</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>OA26FEBRUARI2026</t>
+          <t>JS28NOVEMBER2026</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -6839,23 +6839,23 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA26FEBRUARI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS28NOVEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>oganic</t>
+          <t>jarvis</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>OA27FEBRUARI2026</t>
+          <t>JS29NOVEMBER2026</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -6864,23 +6864,23 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA27FEBRUARI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS29NOVEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>oganic</t>
+          <t>jarvis</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>OA28FEBRUARI2026</t>
+          <t>JS30NOVEMBER2026</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -6889,23 +6889,23 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/OA28FEBRUARI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/JS30NOVEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>oganic</t>
+          <t>jarvis</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>export_raw_to_sheets.py</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>6930</v>
+        <v>14664</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -6914,23 +6914,23 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/export_raw_to_sheets.py</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/jarvis/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>oganic</t>
+          <t>suppasara</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>14664</v>
+        <v>937</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/oganic/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
@@ -6951,11 +6951,11 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>SA01JUNI2026</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>937</v>
+        <v>3850</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA01JUNI2026</t>
         </is>
       </c>
     </row>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>SA01JUNI2026</t>
+          <t>SA02JUNI2026</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -6989,7 +6989,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA01JUNI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA02JUNI2026</t>
         </is>
       </c>
     </row>
@@ -7001,7 +7001,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>SA02JUNI2026</t>
+          <t>SA03JUNI2026</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA02JUNI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA03JUNI2026</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>SA03JUNI2026</t>
+          <t>SA04JUNI2026</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA03JUNI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA04JUNI2026</t>
         </is>
       </c>
     </row>
@@ -7051,7 +7051,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>SA04JUNI2026</t>
+          <t>SA05JUNI2026</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA04JUNI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA05JUNI2026</t>
         </is>
       </c>
     </row>
@@ -7076,7 +7076,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>SA05JUNI2026</t>
+          <t>SA06JUNI2026</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA05JUNI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA06JUNI2026</t>
         </is>
       </c>
     </row>
@@ -7101,7 +7101,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>SA06JUNI2026</t>
+          <t>SA07JUNI2026</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -7114,7 +7114,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA06JUNI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA07JUNI2026</t>
         </is>
       </c>
     </row>
@@ -7126,7 +7126,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>SA07JUNI2026</t>
+          <t>SA08JUNI2026</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -7139,7 +7139,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA07JUNI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA08JUNI2026</t>
         </is>
       </c>
     </row>
@@ -7151,7 +7151,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>SA08JUNI2026</t>
+          <t>SA09JUNI2026</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -7164,7 +7164,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA08JUNI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA09JUNI2026</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>SA09JUNI2026</t>
+          <t>SA10JUNI2026</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA09JUNI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA10JUNI2026</t>
         </is>
       </c>
     </row>
@@ -7201,7 +7201,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>SA10JUNI2026</t>
+          <t>SA11JUNI2026</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA10JUNI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA11JUNI2026</t>
         </is>
       </c>
     </row>
@@ -7226,7 +7226,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>SA11JUNI2026</t>
+          <t>SA12JUNI2026</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA11JUNI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA12JUNI2026</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>SA12JUNI2026</t>
+          <t>SA13JUNI2026</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA12JUNI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA13JUNI2026</t>
         </is>
       </c>
     </row>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>SA13JUNI2026</t>
+          <t>SA14JUNI2026</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA13JUNI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA14JUNI2026</t>
         </is>
       </c>
     </row>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>SA14JUNI2026</t>
+          <t>SA15JUNI2026</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA14JUNI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA15JUNI2026</t>
         </is>
       </c>
     </row>
@@ -7326,7 +7326,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>SA15JUNI2026</t>
+          <t>SA16JUNI2026</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -7339,7 +7339,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA15JUNI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA16JUNI2026</t>
         </is>
       </c>
     </row>
@@ -7351,7 +7351,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>SA16JUNI2026</t>
+          <t>SA17JUNI2026</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA16JUNI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA17JUNI2026</t>
         </is>
       </c>
     </row>
@@ -7376,7 +7376,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>SA17JUNI2026</t>
+          <t>SA18JUNI2026</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -7389,7 +7389,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA17JUNI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA18JUNI2026</t>
         </is>
       </c>
     </row>
@@ -7401,7 +7401,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>SA18JUNI2026</t>
+          <t>SA19JUNI2026</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA18JUNI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA19JUNI2026</t>
         </is>
       </c>
     </row>
@@ -7426,7 +7426,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>SA19JUNI2026</t>
+          <t>SA20JUNI2026</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA19JUNI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA20JUNI2026</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>SA20JUNI2026</t>
+          <t>SA21JUNI2026</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA20JUNI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA21JUNI2026</t>
         </is>
       </c>
     </row>
@@ -7476,7 +7476,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>SA21JUNI2026</t>
+          <t>SA22JUNI2026</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -7489,7 +7489,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA21JUNI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA22JUNI2026</t>
         </is>
       </c>
     </row>
@@ -7501,7 +7501,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>SA22JUNI2026</t>
+          <t>SA23JUNI2026</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -7514,7 +7514,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA22JUNI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA23JUNI2026</t>
         </is>
       </c>
     </row>
@@ -7526,7 +7526,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>SA23JUNI2026</t>
+          <t>SA24JUNI2026</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA23JUNI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA24JUNI2026</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>SA24JUNI2026</t>
+          <t>SA25JUNI2026</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA24JUNI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA25JUNI2026</t>
         </is>
       </c>
     </row>
@@ -7576,7 +7576,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>SA25JUNI2026</t>
+          <t>SA26JUNI2026</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -7589,7 +7589,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA25JUNI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA26JUNI2026</t>
         </is>
       </c>
     </row>
@@ -7601,7 +7601,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>SA26JUNI2026</t>
+          <t>SA27JUNI2026</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -7614,7 +7614,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA26JUNI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA27JUNI2026</t>
         </is>
       </c>
     </row>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>SA27JUNI2026</t>
+          <t>SA28JUNI2026</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA27JUNI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA28JUNI2026</t>
         </is>
       </c>
     </row>
@@ -7651,7 +7651,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>SA28JUNI2026</t>
+          <t>SA29JUNI2026</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA28JUNI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA29JUNI2026</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>SA29JUNI2026</t>
+          <t>SA30JUNI2026</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA29JUNI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA30JUNI2026</t>
         </is>
       </c>
     </row>
@@ -7701,11 +7701,11 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>SA30JUNI2026</t>
+          <t>update_github_file.py</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>3850</v>
+        <v>14659</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -7714,23 +7714,23 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/SA30JUNI2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/update_github_file.py</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>suppasara</t>
+          <t>ester</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>update_github_file.py</t>
+          <t>.github/workflows/main.yml</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>14659</v>
+        <v>933</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -7739,23 +7739,23 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/suppasara/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/.github/workflows/main.yml</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>sintho</t>
+          <t>ester</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>.github/workflows/main.yml</t>
+          <t>ER01DESEMBER2026</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>934</v>
+        <v>588661</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -7764,23 +7764,23 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/.github/workflows/main.yml</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER01DESEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>sintho</t>
+          <t>ester</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>ST01APRIL2026</t>
+          <t>ER02DESEMBER2026</t>
         </is>
       </c>
       <c r="C295" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -7789,23 +7789,23 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST01APRIL2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER02DESEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>sintho</t>
+          <t>ester</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>ST02APRIL2026</t>
+          <t>ER03DESEMBER2026</t>
         </is>
       </c>
       <c r="C296" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -7814,23 +7814,23 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST02APRIL2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER03DESEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>sintho</t>
+          <t>ester</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>ST03APRIL2026</t>
+          <t>ER04DESEMBER2026</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -7839,23 +7839,23 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST03APRIL2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER04DESEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>sintho</t>
+          <t>ester</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>ST04APRIL2026</t>
+          <t>ER05DESEMBER2026</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -7864,23 +7864,23 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST04APRIL2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER05DESEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>sintho</t>
+          <t>ester</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>ST05APRIL2026</t>
+          <t>ER06DESEMBER2026</t>
         </is>
       </c>
       <c r="C299" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -7889,23 +7889,23 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST05APRIL2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER06DESEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>sintho</t>
+          <t>ester</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>ST06APRIL2026</t>
+          <t>ER07DESEMBER2026</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -7914,23 +7914,23 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST06APRIL2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER07DESEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>sintho</t>
+          <t>ester</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>ST07APRIL2026</t>
+          <t>ER08DESEMBER2026</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -7939,23 +7939,23 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST07APRIL2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER08DESEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>sintho</t>
+          <t>ester</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>ST08APRIL2026</t>
+          <t>ER09DESEMBER2026</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -7964,23 +7964,23 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST08APRIL2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER09DESEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>sintho</t>
+          <t>ester</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>ST09APRIL2026</t>
+          <t>ER10DESEMBER2026</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -7989,23 +7989,23 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST09APRIL2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER10DESEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>sintho</t>
+          <t>ester</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>ST10APRIL2026</t>
+          <t>ER11DESEMBER2026</t>
         </is>
       </c>
       <c r="C304" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -8014,23 +8014,23 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST10APRIL2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER11DESEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>sintho</t>
+          <t>ester</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>ST11APRIL2026</t>
+          <t>ER12DESEMBER2026</t>
         </is>
       </c>
       <c r="C305" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -8039,23 +8039,23 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST11APRIL2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER12DESEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>sintho</t>
+          <t>ester</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>ST12APRIL2026</t>
+          <t>ER13DESEMBER2026</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -8064,23 +8064,23 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST12APRIL2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER13DESEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>sintho</t>
+          <t>ester</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>ST13APRIL2026</t>
+          <t>ER14DESEMBER2026</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -8089,23 +8089,23 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST13APRIL2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER14DESEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>sintho</t>
+          <t>ester</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>ST14APRIL2026</t>
+          <t>ER15DESEMBER2026</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -8114,23 +8114,23 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST14APRIL2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER15DESEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>sintho</t>
+          <t>ester</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>ST15APRIL2026</t>
+          <t>ER16DESEMBER2026</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -8139,23 +8139,23 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST15APRIL2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER16DESEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>sintho</t>
+          <t>ester</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>ST16APRIL2026</t>
+          <t>ER17DESEMBER2026</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -8164,23 +8164,23 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST16APRIL2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER17DESEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>sintho</t>
+          <t>ester</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>ST17APRIL2026</t>
+          <t>ER18DESEMBER2026</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -8189,23 +8189,23 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST17APRIL2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER18DESEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>sintho</t>
+          <t>ester</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>ST18APRIL2026</t>
+          <t>ER19DESEMBER2026</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -8214,23 +8214,23 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST18APRIL2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER19DESEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>sintho</t>
+          <t>ester</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>ST19APRIL2026</t>
+          <t>ER20DESEMBER2026</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -8239,23 +8239,23 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST19APRIL2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER20DESEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>sintho</t>
+          <t>ester</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>ST20APRIL2026</t>
+          <t>ER21DESEMBER2026</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -8264,23 +8264,23 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST20APRIL2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER21DESEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>sintho</t>
+          <t>ester</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>ST21APRIL2026</t>
+          <t>ER22DESEMBER2026</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -8289,23 +8289,23 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST21APRIL2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER22DESEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>sintho</t>
+          <t>ester</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>ST22APRIL2026</t>
+          <t>ER23DESEMBER2026</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -8314,23 +8314,23 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST22APRIL2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER23DESEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>sintho</t>
+          <t>ester</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>ST23APRIL2026</t>
+          <t>ER24DESEMBER2026</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -8339,23 +8339,23 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST23APRIL2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER24DESEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>sintho</t>
+          <t>ester</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>ST24APRIL2026</t>
+          <t>ER25DESEMBER2026</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -8364,23 +8364,23 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST24APRIL2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER25DESEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>sintho</t>
+          <t>ester</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>ST25APRIL2026</t>
+          <t>ER26DESEMBER2026</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -8389,23 +8389,23 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST25APRIL2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER26DESEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>sintho</t>
+          <t>ester</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>ST26APRIL2026</t>
+          <t>ER27DESEMBER2026</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -8414,23 +8414,23 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST26APRIL2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER27DESEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>sintho</t>
+          <t>ester</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>ST27APRIL2026</t>
+          <t>ER28DESEMBER2026</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -8439,23 +8439,23 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST27APRIL2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER28DESEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>sintho</t>
+          <t>ester</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>ST28APRIL2026</t>
+          <t>ER29DESEMBER2026</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -8464,23 +8464,23 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST28APRIL2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER29DESEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>sintho</t>
+          <t>ester</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>ST29APRIL2026</t>
+          <t>ER30DESEMBER2026</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -8489,23 +8489,23 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST29APRIL2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER30DESEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>sintho</t>
+          <t>ester</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>ST30APRIL2026</t>
+          <t>ER31DESEMBER2026</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>3850</v>
+        <v>588661</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -8514,14 +8514,14 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/ST30APRIL2026</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/ER31DESEMBER2026</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>sintho</t>
+          <t>ester</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -8530,7 +8530,7 @@
         </is>
       </c>
       <c r="C325" t="n">
-        <v>14658</v>
+        <v>14663</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/uppermoon77/sintho/main/update_github_file.py</t>
+          <t>https://raw.githubusercontent.com/uppermoon77/ester/main/update_github_file.py</t>
         </is>
       </c>
     </row>
